--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportCheck001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportCheck001.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Reaton\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACDF7F7-36F0-4927-8C71-87BEB5FF428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98334367-92CB-4A15-8664-3467B8350FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>报表类别</t>
   </si>
@@ -31,13 +31,16 @@
     <t>产品名称</t>
   </si>
   <si>
-    <t>产品代码</t>
-  </si>
-  <si>
     <t>检查日期</t>
   </si>
   <si>
     <t>错误信息</t>
+  </si>
+  <si>
+    <t>产品主代码</t>
+  </si>
+  <si>
+    <t>子产品代码</t>
   </si>
 </sst>
 </file>
@@ -427,18 +430,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="39.5546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="45.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.88671875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="27.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -449,18 +452,21 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportCheck001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportCheck001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25427"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98334367-92CB-4A15-8664-3467B8350FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +27,6 @@
     <t>报表名称</t>
   </si>
   <si>
-    <t>产品名称</t>
-  </si>
-  <si>
     <t>检查日期</t>
   </si>
   <si>
@@ -41,12 +37,16 @@
   </si>
   <si>
     <t>子产品代码</t>
+  </si>
+  <si>
+    <t>产品全称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -429,19 +429,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="39.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="45.77734375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="27.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="45.75" style="1" customWidth="1"/>
+    <col min="4" max="5" width="27.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="13.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -449,19 +449,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
